--- a/data_extactor/batch_10_fa/trimmed/batch_0031_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0031_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ریاضیات | سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | استراتژی‌های یادگیری | نظارت | نگارش | یادگیری فعال</t>
+          <t>ریاضیات | سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | راهبردهای یادگیری | نظارت | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ریاضیات | آموزش و تدریس | زبان انگلیسی | رایانه و الکترونیک</t>
+          <t>ریاضیات | آموزش و پرورش | زبان انگلیسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>استدلال ریاضی | بیان شفاهی | محاسبات عددی | استدلال قیاسی | درک شفاهی | درک کتبی | استدلال استقرایی</t>
+          <t>استدلال ریاضی | بیان شفاهی | توانایی عددی | استدلال قیاسی | درک شفاهی | درک کتبی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>استادان علوم جوی، زمین، دریا و فضا در دانشگاه‌ها | استادان شیمی در دانشگاه‌ها | استادان علوم کامپیوتر در دانشگاه‌ها | استادان اقتصاد در دانشگاه‌ها | کارشناسان برنامه‌ریزی آموزشی | استادان فیزیک در دانشگاه‌ها | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی و حرفه‌ای</t>
+          <t>استادان و مدرسان علوم جوی، زمین، دریا و فضا در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان شیمی در دانشگاه‌ها و مراکز آموزش عالی | استادان علوم رایانه، آموزش عالی | استادان اقتصاد دانشگاه | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | استادان و مدرسان فیزیک در دانشگاه‌ها و مراکز آموزش عالی | دبیران دوره دوم متوسطه، به‌جز آموزش استثنایی و فنی‌وحرفه‌ای</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | استراتژی‌های یادگیری | نگارش | شنیدن فعال | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>درک مطلب | سخن گفتن | راهبردهای یادگیری | نگارش | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>طراحی | ساختمان و سازه | آموزش و تدریس | رایانه و الکترونیک | هنرهای تجسمی | مهندسی و فناوری</t>
+          <t>طراحی | ساختمان و ساخت‌وساز | آموزش و پرورش | رایانه و الکترونیک | هنرهای زیبا | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | استدلال قیاسی | درک شفاهی | درک کتبی | بیان کتبی | تجسم فضایی</t>
+          <t>بیان شفاهی | وضوح گفتار | استدلال قیاسی | درک شفاهی | درک کتبی | بیان کتبی | تجسم</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مهندسان معمار، به‌جز معماران منظر و مهندسان سازه‌های دریایی | استادان هنر، نمایش و موسیقی در دانشگاه‌ها | استادان آموزش‌های فنی و حرفه‌ای در دانشگاه‌ها | استادان مهندسی در دانشگاه‌ها | کارشناسان برنامه‌ریزی آموزشی | مهندسان معماری منظر | دستیاران آموزشی در دانشگاه‌ها</t>
+          <t>مهندسان معمار، به‌جز معماران منظر و سازه‌های دریایی | مدرسان هنرهای تجسمی، نمایشی و موسیقی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | استادان و مدرسان مهندسی در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مهندسان معمار منظر | دستیاران آموزشی در آموزش عالی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | استراتژی‌های یادگیری | شنیدن فعال | درک مطلب | ریاضیات | تفکر انتقادی | نگارش | یادگیری فعال | مهارت‌های علمی | نظارت</t>
+          <t>سخن گفتن | راهبردهای یادگیری | گوش دادن فعال | درک مطلب | ریاضیات | تفکر انتقادی | نگارش | یادگیری فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | طراحی | رایانه و الکترونیک | ریاضیات | فیزیک | آموزش و تدریس | مکانیک</t>
+          <t>مهندسی و فناوری | طراحی | رایانه و الکترونیک | ریاضیات | فیزیک | آموزش و پرورش | مکانیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مدیران معماری و مهندسی | استادان معماری در دانشگاه‌ها | استادان آموزش‌های فنی و حرفه‌ای در دانشگاه‌ها | استادان علوم کامپیوتر در دانشگاه‌ها | مهندسان صنایع | استادان علوم ریاضی در دانشگاه‌ها | استادان فیزیک در دانشگاه‌ها</t>
+          <t>مدیران فنی و مهندسی و معماری | استادان و مدرسان معماری در دانشگاه‌ها و مراکز آموزش عالی | مدرسان آموزش‌های فنی و حرفه‌ای در آموزش عالی | استادان علوم رایانه، آموزش عالی | مهندسان صنایع | استادان و مدرسان علوم ریاضی در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان فیزیک در دانشگاه‌ها و مراکز آموزش عالی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | استراتژی‌های یادگیری | یادگیری فعال | تفکر انتقادی | نگارش | شنیدن فعال | نظارت | مهارت‌های علمی | ریاضیات</t>
+          <t>درک مطلب | سخن گفتن | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نگارش | گوش دادن فعال | نظارت | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | آموزش و تدریس | مدیریت و امور اداری | تولید و صنایع غذایی | ریاضیات | جغرافیا</t>
+          <t>زیست‌شناسی | آموزش و پرورش | مدیریت و اداره | تولید مواد غذایی | ریاضیات | جغرافیا</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | متخصصان علوم دامی | استادان علوم زیستی در دانشگاه‌ها | زیست‌شناسان | مروجان کشاورزی و اقتصاد خانواده | مدیران مزارع، دامداری‌ها و واحدهای کشاورزی | متخصصان علوم خاک و گیاه‌پزشکی</t>
+          <t>مهندسان کشاورزی | متخصصان علوم دامی | استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | زیست‌شناسان | کارشناسان ترویج و آموزش کشاورزی و اقتصاد خانواده | مدیران امور کشاورزی، دامپروری و شیلات | متخصصان خاک‌شناسی و علوم گیاهی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | استراتژی‌های یادگیری | یادگیری فعال | مهارت‌های علمی | نگارش | شنیدن فعال | درک مطلب | تفکر انتقادی | نظارت | ریاضیات</t>
+          <t>سخن گفتن | راهبردهای یادگیری | یادگیری فعال | علوم | نگارش | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | ریاضیات | شیمی | آموزش و تدریس | رایانه و الکترونیک | پزشکی و دندانپزشکی</t>
+          <t>زیست‌شناسی | ریاضیات | شیمی | آموزش و پرورش | رایانه و الکترونیک | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>بیوشیمی‌دانان و بیوفیزیک‌دانان | تکنسین‌های زیست‌شناسی | زیست‌شناسان | استادان شیمی در دانشگاه‌ها | متخصصان ژنتیک | استادان علوم پزشکی و بهداشت در دانشگاه‌ها | زیست‌شناسان سلولی و مولکولی</t>
+          <t>زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | تکنسین‌های علوم زیستی | زیست‌شناسان | استادان و مدرسان شیمی در دانشگاه‌ها و مراکز آموزش عالی | متخصصان ژنتیک | استادان تخصص‌های علوم پزشکی و بهداشت دانشگاه | زیست‌شناسان سلولی و مولکولی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>استراتژی‌های یادگیری | درک مطلب | نگارش | سخن گفتن | شنیدن فعال | یادگیری فعال | تفکر انتقادی | نظارت | مهارت‌های علمی | ریاضیات</t>
+          <t>راهبردهای یادگیری | درک مطلب | نگارش | سخن گفتن | گوش دادن فعال | یادگیری فعال | تفکر انتقادی | نظارت | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | ریاضیات | زیست‌شناسی | رایانه و الکترونیک | جغرافیا | مدیریت و امور اداری</t>
+          <t>آموزش و پرورش | ریاضیات | زیست‌شناسی | رایانه و الکترونیک | جغرافیا | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>استادان علوم کشاورزی در دانشگاه‌ها | استادان علوم زیستی در دانشگاه‌ها | زیست‌شناسان | کارشناسان حفاظت از منابع طبیعی و جنگل‌داری | استادان علوم محیط‌زیست در دانشگاه‌ها | استادان جغرافیا در دانشگاه‌ها | مدیران علوم طبیعی</t>
+          <t>استادان و مدرسان علوم کشاورزی در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | زیست‌شناسان | دانشمندان حفاظت از منابع طبیعی | استادان و مدرسان علوم محیط‌زیست در دانشگاه‌ها و مراکز آموزش عالی | استادان جغرافیای دانشگاه | مدیران علوم طبیعی و پایه‌ای</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,12 +850,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | تفکر انتقادی | مهارت‌های علمی | نگارش | شنیدن فعال | یادگیری فعال | استراتژی‌های یادگیری | نظارت | ریاضیات</t>
+          <t>سخن گفتن | درک مطلب | تفکر انتقادی | علوم | نگارش | گوش دادن فعال | یادگیری فعال | راهبردهای یادگیری | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | ریاضیات | فیزیک | شیمی | رایانه و الکترونیک | جغرافیا</t>
+          <t>آموزش و پرورش | ریاضیات | فیزیک | شیمی | رایانه و الکترونیک | جغرافیا</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>استادان علوم زیستی در دانشگاه‌ها | استادان شیمی در دانشگاه‌ها | استادان مهندسی در دانشگاه‌ها | استادان علوم محیط‌زیست در دانشگاه‌ها | استادان جغرافیا در دانشگاه‌ها | استادان علوم ریاضی در دانشگاه‌ها | استادان فیزیک در دانشگاه‌ها</t>
+          <t>استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان شیمی در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان مهندسی در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان علوم محیط‌زیست در دانشگاه‌ها و مراکز آموزش عالی | استادان جغرافیای دانشگاه | استادان و مدرسان علوم ریاضی در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان فیزیک در دانشگاه‌ها و مراکز آموزش عالی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | نگارش | نظارت | استراتژی‌های یادگیری | یادگیری فعال | تفکر انتقادی | مهارت‌های علمی | شنیدن فعال | ریاضیات</t>
+          <t>درک مطلب | سخن گفتن | نگارش | نظارت | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | علوم | گوش دادن فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>شیمی | ریاضیات | آموزش و تدریس | زیست‌شناسی | فیزیک | مهندسی و فناوری</t>
+          <t>شیمی | ریاضیات | آموزش و پرورش | زیست‌شناسی | فیزیک | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>بیوشیمی‌دانان و بیوفیزیک‌دانان | استادان علوم زیستی در دانشگاه‌ها | تکنسین‌های شیمی | شیمیدانان | استادان مهندسی در دانشگاه‌ها | استادان علوم ریاضی در دانشگاه‌ها | استادان فیزیک در دانشگاه‌ها</t>
+          <t>زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | تکنسین‌های شیمی | شیمی‌دانان | استادان و مدرسان مهندسی در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان علوم ریاضی در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان فیزیک در دانشگاه‌ها و مراکز آموزش عالی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | تفکر انتقادی | مهارت‌های علمی | نگارش | شنیدن فعال | استراتژی‌های یادگیری | یادگیری فعال | نظارت | ریاضیات</t>
+          <t>درک مطلب | سخن گفتن | تفکر انتقادی | علوم | نگارش | گوش دادن فعال | راهبردهای یادگیری | یادگیری فعال | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>آموزش و تدریس | زیست‌شناسی | شیمی | ریاضیات | جغرافیا | مهندسی و فناوری</t>
+          <t>آموزش و پرورش | زیست‌شناسی | شیمی | ریاضیات | جغرافیا | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>استادان علوم زیستی در دانشگاه‌ها | زیست‌شناسان | کارشناسان حفاظت از منابع طبیعی و جنگل‌داری | کارشناسان و متخصصان علوم محیط‌زیست و بهداشت محیط | استادان جنگلداری و حفاظت از منابع طبیعی در دانشگاه‌ها | استادان جغرافیا در دانشگاه‌ها | مدیران علوم طبیعی</t>
+          <t>استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | زیست‌شناسان | دانشمندان حفاظت از منابع طبیعی | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | استادان و مدرسان جنگلداری و منابع طبیعی در دانشگاه‌ها و مراکز آموزش عالی | استادان جغرافیای دانشگاه | مدیران علوم طبیعی و پایه‌ای</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | مهارت‌های علمی | استراتژی‌های یادگیری | یادگیری فعال | تفکر انتقادی | نگارش | شنیدن فعال | ریاضیات | نظارت</t>
+          <t>درک مطلب | سخن گفتن | علوم | راهبردهای یادگیری | یادگیری فعال | تفکر انتقادی | نگارش | گوش دادن فعال | ریاضیات | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ریاضیات | فیزیک | آموزش و تدریس | زبان انگلیسی | رایانه و الکترونیک | شیمی | مهندسی و فناوری</t>
+          <t>ریاضیات | فیزیک | آموزش و پرورش | زبان انگلیسی | رایانه و الکترونیک | شیمی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>اخترشناسان | استادان علوم جوی، زمین، دریا و فضا در دانشگاه‌ها | استادان شیمی در دانشگاه‌ها | استادان مهندسی در دانشگاه‌ها | استادان علوم ریاضی در دانشگاه‌ها | ریاضیدانان | فیزیکدانان</t>
+          <t>ستاره‌شناسان و اخترشناسان | استادان و مدرسان علوم جوی، زمین، دریا و فضا در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان شیمی در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان مهندسی در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان علوم ریاضی در دانشگاه‌ها و مراکز آموزش عالی | ریاضی‌دانان | فیزیک‌دانان</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
